--- a/backend/toolbox/持仓比例.xlsx
+++ b/backend/toolbox/持仓比例.xlsx
@@ -1,21 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A290E6EB-DCDB-4539-AC5D-DF8096EFF67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="0" windowWidth="19020" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4056" yWindow="0" windowWidth="18984" windowHeight="12336"/>
   </bookViews>
   <sheets>
     <sheet name="持仓比例" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t>类型</t>
   </si>
@@ -60,9 +58,6 @@
     <t>类型比例</t>
   </si>
   <si>
-    <t>稳健</t>
-  </si>
-  <si>
     <t>互联网</t>
   </si>
   <si>
@@ -276,10 +271,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>激进</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>消费</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -392,174 +383,280 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>440.0</t>
-  </si>
-  <si>
-    <t>119.9</t>
-  </si>
-  <si>
-    <t>44.72</t>
-  </si>
-  <si>
-    <t>32.53</t>
-  </si>
-  <si>
-    <t>28.27</t>
-  </si>
-  <si>
-    <t>88.9</t>
-  </si>
-  <si>
-    <t>88.25</t>
-  </si>
-  <si>
-    <t>393.93</t>
-  </si>
-  <si>
-    <t>21.16</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>6.8</t>
-  </si>
-  <si>
-    <t>45.14</t>
-  </si>
-  <si>
-    <t>11.47</t>
-  </si>
-  <si>
-    <t>2.484</t>
-  </si>
-  <si>
-    <t>84.79</t>
-  </si>
-  <si>
-    <t>589.85</t>
-  </si>
-  <si>
-    <t>343.54</t>
-  </si>
-  <si>
-    <t>495.4</t>
-  </si>
-  <si>
-    <t>342.27</t>
-  </si>
-  <si>
-    <t>102.5</t>
-  </si>
-  <si>
-    <t>971.66</t>
-  </si>
-  <si>
-    <t>148.47</t>
-  </si>
-  <si>
-    <t>20260815</t>
-  </si>
-  <si>
     <t>潜在50%涨幅</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>A股</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>00981</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>中芯国际</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.075</t>
+  </si>
+  <si>
+    <t>4%+回报</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>国产替代</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>超额</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>51.21</t>
+  </si>
+  <si>
+    <t>82.76</t>
+  </si>
+  <si>
+    <t>0.685</t>
+  </si>
+  <si>
+    <t>49.84</t>
+  </si>
+  <si>
+    <t>705.44</t>
+  </si>
+  <si>
+    <t>533.52</t>
+  </si>
+  <si>
+    <t>374.8</t>
+  </si>
+  <si>
+    <t>98.0</t>
+  </si>
+  <si>
+    <t>79.17</t>
+  </si>
+  <si>
+    <t>49.5</t>
+  </si>
+  <si>
+    <t>27.78</t>
+  </si>
+  <si>
+    <t>21.4</t>
+  </si>
+  <si>
+    <t>79.86</t>
+  </si>
+  <si>
+    <t>67.1</t>
+  </si>
+  <si>
+    <t>220.0</t>
+  </si>
+  <si>
+    <t>28.0</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>44.8</t>
+  </si>
+  <si>
+    <t>45.8</t>
+  </si>
+  <si>
+    <t>7.745</t>
+  </si>
+  <si>
+    <t>648.85</t>
+  </si>
+  <si>
+    <t>320.76</t>
+  </si>
+  <si>
+    <t>521.08</t>
+  </si>
+  <si>
+    <t>374.58</t>
+  </si>
+  <si>
+    <t>85.49</t>
+  </si>
+  <si>
+    <t>856.49</t>
+  </si>
+  <si>
+    <t>169.09</t>
+  </si>
+  <si>
+    <t>2.408</t>
+  </si>
+  <si>
+    <t>20261023</t>
+  </si>
+  <si>
+    <t>381.8</t>
+  </si>
+  <si>
+    <t>98.5</t>
+  </si>
+  <si>
+    <t>50.68</t>
+  </si>
+  <si>
+    <t>27.3</t>
+  </si>
+  <si>
+    <t>21.38</t>
+  </si>
+  <si>
+    <t>79.79</t>
+  </si>
+  <si>
+    <t>67.4</t>
+  </si>
+  <si>
+    <t>216.16</t>
+  </si>
+  <si>
+    <t>27.98</t>
+  </si>
+  <si>
+    <t>44.88</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>49.07</t>
+  </si>
+  <si>
+    <t>26.99</t>
+  </si>
+  <si>
+    <t>21.42</t>
+  </si>
+  <si>
+    <t>79.5</t>
+  </si>
+  <si>
+    <t>2.398</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="10"/>
-      <name val="等线"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="10"/>
-      <name val="等线"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="10"/>
-      <name val="等线"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="2"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="10"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="10"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="0" tint="-0.3499862666707358"/>
       <sz val="10"/>
-      <color theme="0" tint="-0.34998626667073579"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="0" tint="-0.3499862666707358"/>
       <sz val="10"/>
-      <color theme="0" tint="-0.34998626667073579"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
+      <family val="3"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -573,13 +670,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8CDDFA"/>
-        <bgColor auto="1"/>
+        <bgColor auto="true"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor auto="1"/>
+        <bgColor auto="true"/>
       </patternFill>
     </fill>
     <fill>
@@ -590,13 +687,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor auto="1"/>
+        <bgColor auto="true"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="none">
-        <fgColor auto="1"/>
-        <bgColor auto="1"/>
+        <fgColor auto="true"/>
+        <bgColor auto="true"/>
       </patternFill>
     </fill>
     <fill>
@@ -606,8 +703,8 @@
     </fill>
     <fill>
       <patternFill patternType="none">
-        <fgColor auto="1"/>
-        <bgColor auto="1"/>
+        <fgColor auto="true"/>
+        <bgColor auto="true"/>
       </patternFill>
     </fill>
     <fill>
@@ -618,7 +715,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF9A38D7"/>
-        <bgColor auto="1"/>
+        <bgColor auto="true"/>
       </patternFill>
     </fill>
     <fill>
@@ -662,162 +759,180 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="9" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -830,7 +945,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1127,24 +1242,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="持仓比例"/>
-  <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultColWidth="13.64453125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr defaultColWidth="13.64453125" defaultRowHeight="18" customHeight="true"/>
   <cols>
-    <col min="1" max="1" width="13.9375" style="18" customWidth="1"/>
-    <col min="2" max="2" width="13.9375" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.9375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.41015625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.46875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.05859375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5859375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.8203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.46875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.17578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="8.8203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.05859375" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" style="18" width="14.87890625"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" style="18" width="13.9375"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="10.9375"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" style="15" width="9.41015625"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="8.46875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="7.05859375"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="8.5859375"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="8.8203125"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="6.46875"/>
+    <col bestFit="true" customWidth="true" max="10" min="10" width="8.17578125"/>
+    <col bestFit="true" customWidth="true" max="14" min="11" width="8.8203125"/>
+    <col bestFit="true" customWidth="true" max="15" min="15" width="12.05859375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" ht="18" customHeight="true">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1155,19 +1270,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>4</v>
@@ -1185,108 +1300,98 @@
         <v>8</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="43" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="18" customHeight="true">
+      <c r="A2" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
       <c r="D2" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="F2">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="G2" s="4">
-        <f>E2*F2*C30</f>
-        <v>567375.6</v>
-      </c>
-      <c r="H2" s="38">
+        <f>E2*F2*C31</f>
+      </c>
+      <c r="H2" s="43">
         <f>SUM(G2:G4)</f>
-        <v>1237170.4753416001</v>
       </c>
       <c r="I2" s="5">
-        <f>G2/G26</f>
-        <v>0.18752008051444546</v>
+        <f>G2/G27</f>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="5">
-        <f>G2/G28</f>
-        <v>0.43613036068641625</v>
+        <f>G2/G29</f>
       </c>
       <c r="L2" s="7"/>
-      <c r="M2" s="32">
-        <f>H2/G26</f>
-        <v>0.40889017283462958</v>
+      <c r="M2" s="47">
+        <f>H2/G27</f>
       </c>
       <c r="N2" s="11">
-        <f>SUM(G16:G23)/G26</f>
-        <v>0.20284760460817483</v>
+        <f>SUM(G17:G24)/G27</f>
       </c>
       <c r="O2" s="11">
-        <f>SUM(G2:G3,G16:G21)/G26</f>
-        <v>0.44594929382515175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="44"/>
-      <c r="B3" s="46"/>
+        <f>SUM(G2:G3,G15,G17:G19,G21:G22)/G27</f>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="18" customHeight="true">
+      <c r="A3" s="39"/>
+      <c r="B3" s="37"/>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="F3">
         <v>5100</v>
       </c>
       <c r="G3" s="4">
-        <f>E3*F3*C30</f>
-        <v>525673.49340000004</v>
-      </c>
-      <c r="H3" s="33"/>
+        <f>E3*F3*C31</f>
+      </c>
+      <c r="H3" s="35"/>
       <c r="I3" s="5">
-        <f>G3/G26</f>
-        <v>0.17373735459663375</v>
+        <f>G3/G27</f>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="5">
-        <f>G3/G28</f>
-        <v>0.40407477917596474</v>
+        <f>G3/G29</f>
       </c>
       <c r="L3" s="7"/>
-      <c r="M3" s="33"/>
+      <c r="M3" s="35"/>
       <c r="N3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O3" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="44"/>
-      <c r="B4" s="46"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="18" customHeight="true">
+      <c r="A4" s="39"/>
+      <c r="B4" s="37"/>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>
@@ -1295,876 +1400,804 @@
         <v>252</v>
       </c>
       <c r="G4" s="4">
-        <f>E4*F4*C31</f>
-        <v>144121.3819416</v>
-      </c>
-      <c r="H4" s="33"/>
+        <f>E4*F4*C32</f>
+      </c>
+      <c r="H4" s="35"/>
       <c r="I4" s="5">
-        <f>G4/G26</f>
-        <v>4.7632737723550297E-2</v>
+        <f>G4/G27</f>
       </c>
       <c r="J4" s="6"/>
       <c r="L4" s="5">
-        <f>G4/G29</f>
-        <v>0.1901655725959828</v>
-      </c>
-      <c r="M4" s="33"/>
+        <f>G4/G30</f>
+      </c>
+      <c r="M4" s="35"/>
       <c r="N4" s="11">
-        <f>SUM(G2:G4,G15)/G26</f>
-        <v>0.42746574153759009</v>
+        <f>SUM(G2:G4,G15:G16)/G27</f>
       </c>
       <c r="O4" s="11">
-        <f>SUM(G7,G8:G10,G15)/G26</f>
-        <v>0.18402932412694234</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="44"/>
-      <c r="B5" s="42" t="s">
+        <f>SUM(G7,G8:G10,G16,G20)/G27</f>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="18" customHeight="true">
+      <c r="A5" s="39"/>
+      <c r="B5" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F5" s="23">
         <v>0</v>
       </c>
       <c r="G5" s="25">
         <f>E5*F5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="47">
+      </c>
+      <c r="H5" s="44">
         <f>SUM(G5:G7)</f>
-        <v>140421</v>
       </c>
       <c r="I5" s="5">
-        <f>G5/G26</f>
-        <v>0</v>
+        <f>G5/G27</f>
       </c>
       <c r="J5" s="5">
-        <f>G5/G27</f>
-        <v>0</v>
+        <f>G5/G28</f>
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="31">
-        <f>H5/G26</f>
-        <v>4.6409745547603652E-2</v>
+      <c r="M5" s="46">
+        <f>H5/G27</f>
       </c>
       <c r="N5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O5" s="26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="44"/>
-      <c r="B6" s="42"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="18" customHeight="true">
+      <c r="A6" s="39"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="F6" s="19">
         <v>3100</v>
       </c>
       <c r="G6" s="21">
         <f>E6*F6</f>
-        <v>100843</v>
-      </c>
-      <c r="H6" s="48"/>
+      </c>
+      <c r="H6" s="45"/>
       <c r="I6" s="5">
-        <f>G6/G26</f>
-        <v>3.3329046013466611E-2</v>
+        <f>G6/G27</f>
       </c>
       <c r="J6" s="5">
-        <f>G6/G27</f>
-        <v>0.16766564195924344</v>
+        <f>G6/G28</f>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="31"/>
+      <c r="M6" s="46"/>
       <c r="N6" s="11">
-        <f>SUM(G16:G21)/G26</f>
-        <v>8.469185871407256E-2</v>
+        <f>SUM(G17:G22)/G27</f>
       </c>
       <c r="O6" s="12">
-        <f>SUM(G2:G3,G16:G18)/G26</f>
-        <v>0.36125743511107927</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="40"/>
-      <c r="B7" s="42"/>
+        <f>SUM(G2:G3,G17:G19)/G27</f>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="18" customHeight="true">
+      <c r="A7" s="39"/>
+      <c r="B7" s="56"/>
       <c r="C7" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="F7" s="19">
-        <v>1400</v>
+        <v>2900</v>
       </c>
       <c r="G7" s="21">
         <f>E7*F7</f>
-        <v>39578</v>
-      </c>
-      <c r="H7" s="48"/>
+      </c>
+      <c r="H7" s="45"/>
       <c r="I7" s="5">
-        <f>G7/G26</f>
-        <v>1.308069953413704E-2</v>
+        <f>G7/G27</f>
       </c>
       <c r="J7" s="5">
-        <f>G7/G27</f>
-        <v>6.5803980221363273E-2</v>
+        <f>G7/G28</f>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="5"/>
-      <c r="M7" s="31"/>
+      <c r="M7" s="46"/>
       <c r="N7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O7" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="44"/>
-      <c r="B8" s="43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="18" customHeight="true">
+      <c r="A8" s="39"/>
+      <c r="B8" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>18</v>
-      </c>
       <c r="D8" s="24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="F8" s="23">
         <v>0</v>
       </c>
       <c r="G8" s="25">
         <f>E8*F8</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="38">
+      </c>
+      <c r="H8" s="43">
         <f>SUM(G8:G10)</f>
-        <v>461031.98</v>
       </c>
       <c r="I8" s="5">
-        <f>G8/G26</f>
-        <v>0</v>
+        <f>G8/G27</f>
       </c>
       <c r="J8" s="5">
-        <f>G8/G27</f>
-        <v>0</v>
+        <f>G8/G28</f>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="34">
-        <f>H8/G26</f>
-        <v>0.15237305588984479</v>
+      <c r="M8" s="48">
+        <f>H8/G27</f>
       </c>
       <c r="N8" s="8">
-        <f>SUM(G5:G7,G22)/G26</f>
-        <v>8.0169497564312645E-2</v>
+        <f>SUM(G5:G7,G23)/G27</f>
       </c>
       <c r="O8" s="8">
-        <f>SUM(G20:G21)/G26</f>
-        <v>7.1720719401126065E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="40"/>
-      <c r="B9" s="35"/>
+        <f>SUM(G15,G21:G22)/G27</f>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="18" customHeight="true">
+      <c r="A9" s="39"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>70</v>
-      </c>
       <c r="E9" s="19" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="F9" s="19">
         <v>4000</v>
       </c>
       <c r="G9" s="21">
-        <f>E9*F9*C30</f>
-        <v>303459.98</v>
-      </c>
-      <c r="H9" s="38"/>
+        <f>E9*F9*C31</f>
+      </c>
+      <c r="H9" s="43"/>
       <c r="I9" s="5">
-        <f>G9/G26</f>
-        <v>0.10029483094181704</v>
+        <f>G9/G27</f>
       </c>
       <c r="J9" s="5">
-        <f>G9/G27</f>
-        <v>0.5045448108013364</v>
+        <f>G9/G28</f>
       </c>
       <c r="L9" s="7"/>
-      <c r="M9" s="34"/>
+      <c r="M9" s="48"/>
       <c r="N9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O9" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="18" customHeight="true">
+      <c r="A10" s="39"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="19" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="40"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="D10" s="20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="F10" s="19">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G10" s="21">
         <f>E10*F10</f>
-        <v>157572</v>
-      </c>
-      <c r="H10" s="38"/>
+      </c>
+      <c r="H10" s="43"/>
       <c r="I10" s="5">
-        <f>G10/G26</f>
-        <v>5.2078224948027732E-2</v>
+        <f>G10/G27</f>
       </c>
       <c r="J10" s="5">
-        <f>G10/G27</f>
-        <v>0.26198556701805686</v>
+        <f>G10/G28</f>
       </c>
       <c r="L10" s="7"/>
-      <c r="M10" s="34"/>
+      <c r="M10" s="48"/>
       <c r="N10" s="8">
-        <f>SUM(G8:G10)/G26</f>
-        <v>0.15237305588984479</v>
+        <f>SUM(G8:G10)/G27</f>
       </c>
       <c r="O10" s="8">
-        <f>SUM(G2:G4,G13)/G26</f>
-        <v>0.43497251130618425</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F11" s="19">
-        <v>4000</v>
-      </c>
-      <c r="G11" s="21">
-        <f>E11*F11*C30</f>
-        <v>72761.622399999993</v>
-      </c>
-      <c r="H11" s="41">
-        <f>SUM(G11:G15)</f>
-        <v>207882.12153999999</v>
+        <f>SUM(G2:G4,G13)/G27</f>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="18" customHeight="true">
+      <c r="A11" s="39"/>
+      <c r="B11" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="23">
+        <v>0</v>
+      </c>
+      <c r="G11" s="25">
+        <f>E11*F11*C31</f>
+      </c>
+      <c r="H11" s="54">
+        <f>SUM(G11:G16)</f>
       </c>
       <c r="I11" s="5">
-        <f>G11/G26</f>
-        <v>2.4048029719307067E-2</v>
+        <f>G11/G27</f>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="5">
-        <f>G11/G28</f>
-        <v>5.5930414740148898E-2</v>
+        <f>G11/G29</f>
       </c>
       <c r="L11" s="7"/>
-      <c r="M11" s="36">
-        <f>H11/G26</f>
-        <v>6.8705936893822261E-2</v>
+      <c r="M11" s="49">
+        <f>H11/G27</f>
       </c>
       <c r="N11" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O11" s="26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="43"/>
-      <c r="B12" s="39"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="18" customHeight="true">
+      <c r="A12" s="39"/>
+      <c r="B12" s="52"/>
       <c r="C12" s="23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F12" s="23">
         <v>0</v>
       </c>
       <c r="G12" s="25">
-        <f>E12*F12*C30</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="41"/>
+        <f>E12*F12*C31</f>
+      </c>
+      <c r="H12" s="54"/>
       <c r="I12" s="5">
-        <f>G12/G26</f>
-        <v>0</v>
+        <f>G12/G27</f>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="5">
-        <f>G12/G28</f>
-        <v>0</v>
+        <f>G12/G29</f>
       </c>
       <c r="L12" s="7"/>
-      <c r="M12" s="36"/>
+      <c r="M12" s="49"/>
       <c r="N12" s="8">
-        <f>SUM(G4,G11:G12)/G26</f>
-        <v>7.1680767442857368E-2</v>
+        <f>SUM(G4,G11:G12)/G27</f>
       </c>
       <c r="O12" s="8">
-        <f>SUM(G2:G3,G9)/G26</f>
-        <v>0.46155226605289634</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="43"/>
-      <c r="B13" s="40" t="s">
-        <v>73</v>
+        <f>SUM(G2:G3,G9)/G27</f>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="18" customHeight="true">
+      <c r="A13" s="39"/>
+      <c r="B13" s="53" t="s">
+        <v>71</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F13" s="19">
-        <v>13500</v>
+        <v>11600</v>
       </c>
       <c r="G13" s="21">
-        <f>E13*F13*C30</f>
-        <v>78916.788</v>
-      </c>
-      <c r="H13" s="41"/>
+        <f>E13*F13*C31</f>
+      </c>
+      <c r="H13" s="54"/>
       <c r="I13" s="5">
-        <f>G13/G26</f>
-        <v>2.6082338471554691E-2</v>
+        <f>G13/G27</f>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="5">
-        <f>G13/G28</f>
-        <v>6.0661768350019719E-2</v>
+        <f>G13/G29</f>
       </c>
       <c r="L13" s="7"/>
-      <c r="M13" s="36"/>
+      <c r="M13" s="49"/>
       <c r="N13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O13" s="26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="43"/>
-      <c r="B14" s="40"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="18" customHeight="true">
+      <c r="A14" s="39"/>
+      <c r="B14" s="53"/>
       <c r="C14" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F14" s="23">
         <v>0</v>
       </c>
       <c r="G14" s="25">
-        <f>E14*F14*C30</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="41"/>
+        <f>E14*F14*C31</f>
+      </c>
+      <c r="H14" s="54"/>
       <c r="I14" s="5">
-        <f>G14/G26</f>
-        <v>0</v>
+        <f>G14/G27</f>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="5">
-        <f>G14/G28</f>
-        <v>0</v>
+        <f>G14/G29</f>
       </c>
       <c r="L14" s="7"/>
-      <c r="M14" s="36"/>
+      <c r="M14" s="49"/>
       <c r="N14" s="8">
-        <f>SUM(G13:G14)/G26</f>
-        <v>2.6082338471554691E-2</v>
+        <f>SUM(G13:G14)/G27</f>
       </c>
       <c r="O14" s="8">
-        <f>SUM(G3,G4,G7,G9,G10,G11,G15,G20,G22)/G26</f>
-        <v>0.52193143160589472</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="43"/>
-      <c r="B15" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="19">
-        <v>5700</v>
-      </c>
-      <c r="G15" s="21">
-        <f>E15*F15*C30</f>
-        <v>56203.711140000007</v>
-      </c>
-      <c r="H15" s="41"/>
+        <f>SUM(G3,G4,G7,G9,G10,G11,G15,G16,G21,G23)/G27</f>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="18" customHeight="true">
+      <c r="A15" s="40"/>
+      <c r="B15" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="F15" s="31">
+        <v>2500</v>
+      </c>
+      <c r="G15" s="25">
+        <f>E15*F15*C31</f>
+      </c>
+      <c r="H15" s="55"/>
       <c r="I15" s="5">
-        <f>G15/G26</f>
-        <v>1.8575568702960503E-2</v>
+        <f>G15/G27</f>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="5">
-        <f>G15/G28</f>
-        <v>4.3202677047450323E-2</v>
+        <f>G15/G29</f>
       </c>
       <c r="L15" s="7"/>
-      <c r="M15" s="36"/>
-    </row>
-    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="23">
-        <v>0</v>
-      </c>
-      <c r="G16" s="25">
+      <c r="M15" s="50"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="18" customHeight="true">
+      <c r="A16" s="39"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="19">
+        <v>5700</v>
+      </c>
+      <c r="G16" s="21">
         <f>E16*F16*C31</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="38">
-        <f>SUM(G16:G21)</f>
-        <v>256250.39207100001</v>
-      </c>
+      </c>
+      <c r="H16" s="54"/>
       <c r="I16" s="5">
-        <f>G16/G26</f>
-        <v>0</v>
+        <f>G16/G27</f>
       </c>
       <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="5">
+      <c r="K16" s="5">
         <f>G16/G29</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="37">
-        <f>H16/G26</f>
-        <v>8.469185871407256E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="35"/>
-      <c r="B17" s="35"/>
+      </c>
+      <c r="L16" s="7"/>
+      <c r="M16" s="49"/>
+      <c r="O16" s="8">
+        <f>SUM(G10)/G27</f>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="18" customHeight="true">
+      <c r="A17" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>75</v>
+      </c>
       <c r="C17" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F17" s="23">
         <v>0</v>
       </c>
       <c r="G17" s="25">
-        <f>E17*F17*C31</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="38"/>
+        <f>E17*F17*C32</f>
+      </c>
+      <c r="H17" s="43">
+        <f>SUM(G17:G22)</f>
+      </c>
       <c r="I17" s="5">
-        <f>G17/G26</f>
-        <v>0</v>
+        <f>G17/G27</f>
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
       <c r="L17" s="5">
-        <f>G17/G29</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="37"/>
-    </row>
-    <row r="18" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="35"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F18" s="23">
-        <v>0</v>
-      </c>
-      <c r="G18" s="25">
-        <f>E18*F18*C31</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="38"/>
+        <f>G17/G30</f>
+      </c>
+      <c r="M17" s="51">
+        <f>H17/G27</f>
+      </c>
+      <c r="O17" s="26" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="18" customHeight="true">
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" s="31">
+        <v>18</v>
+      </c>
+      <c r="G18" s="4">
+        <f>E18*F18*C32</f>
+      </c>
+      <c r="H18" s="43"/>
       <c r="I18" s="5">
-        <f>G18/G26</f>
-        <v>0</v>
+        <f>G18/G27</f>
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="5">
-        <f>G18/G29</f>
+        <f>G18/G30</f>
+      </c>
+      <c r="M18" s="51"/>
+      <c r="O18" s="8">
+        <f>SUM(G11,G13,G15,G16)/G27</f>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="18" customHeight="true">
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" s="23">
         <v>0</v>
       </c>
-      <c r="M18" s="37"/>
-    </row>
-    <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="35"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="19">
-        <v>17</v>
-      </c>
-      <c r="G19" s="21">
-        <f>E19*F19*C31</f>
-        <v>39246.505921800002</v>
-      </c>
-      <c r="H19" s="38"/>
+      <c r="G19" s="25">
+        <f>E19*F19*C32</f>
+      </c>
+      <c r="H19" s="43"/>
       <c r="I19" s="5">
-        <f>G19/G26</f>
-        <v>1.2971139312946483E-2</v>
+        <f>G19/G27</f>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="5">
-        <f>G19/G29</f>
-        <v>5.1785059027778226E-2</v>
-      </c>
-      <c r="M19" s="37"/>
-    </row>
-    <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="35"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="F20" s="19">
-        <v>257</v>
-      </c>
-      <c r="G20" s="21">
-        <f>E20*F20*C31</f>
-        <v>177680.68935</v>
-      </c>
-      <c r="H20" s="38"/>
+        <f>G19/G30</f>
+      </c>
+      <c r="M19" s="51"/>
+    </row>
+    <row r="20" spans="1:15" ht="18" customHeight="true">
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="23">
+        <v>0</v>
+      </c>
+      <c r="G20" s="25">
+        <f>E20*F20*C32</f>
+      </c>
+      <c r="H20" s="43"/>
       <c r="I20" s="5">
-        <f>G20/G26</f>
-        <v>5.8724233422752362E-2</v>
+        <f>G20/G27</f>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="5">
-        <f>G20/G29</f>
-        <v>0.23444647542432923</v>
-      </c>
-      <c r="M20" s="37"/>
-    </row>
-    <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="35"/>
-      <c r="B21" s="35"/>
+        <f>G20/G30</f>
+      </c>
+      <c r="M20" s="51"/>
+    </row>
+    <row r="21" spans="1:15" ht="18" customHeight="true">
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
       <c r="C21" s="19" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F21" s="19">
-        <v>6</v>
+        <v>257</v>
       </c>
       <c r="G21" s="21">
-        <f>E21*F21*C31</f>
-        <v>39323.196799199999</v>
-      </c>
-      <c r="H21" s="38"/>
+        <f>E21*F21*C32</f>
+      </c>
+      <c r="H21" s="43"/>
       <c r="I21" s="5">
-        <f>G21/G26</f>
-        <v>1.2996485978373707E-2</v>
+        <f>G21/G27</f>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="5">
-        <f>G21/G29</f>
-        <v>5.1886251261832494E-2</v>
-      </c>
-      <c r="M21" s="37"/>
-    </row>
-    <row r="22" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="35"/>
-      <c r="B22" s="28" t="s">
-        <v>25</v>
-      </c>
+        <f>G21/G30</f>
+      </c>
+      <c r="M21" s="51"/>
+    </row>
+    <row r="22" spans="1:15" ht="18" customHeight="true">
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
       <c r="C22" s="19" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F22" s="19">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="G22" s="21">
-        <f>E22*F22*C31</f>
-        <v>102146.17817880001</v>
-      </c>
-      <c r="H22" s="29">
-        <f>SUM(G22:G22)</f>
-        <v>102146.17817880001</v>
-      </c>
+        <f>E22*F22*C32</f>
+      </c>
+      <c r="H22" s="43"/>
       <c r="I22" s="5">
-        <f>G22/G26</f>
-        <v>3.3759752016708985E-2</v>
+        <f>G22/G27</f>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="5">
-        <f>G22/G29</f>
-        <v>0.1347800458209174</v>
-      </c>
-      <c r="M22" s="30">
-        <f>H22/G26</f>
-        <v>3.3759752016708985E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="35"/>
-      <c r="B23" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" t="s">
-        <v>113</v>
-      </c>
-      <c r="F23">
-        <v>102800</v>
-      </c>
-      <c r="G23" s="4">
-        <f>E23*F23</f>
-        <v>255355.2</v>
-      </c>
-      <c r="H23" s="4">
-        <f>SUM(G23)</f>
-        <v>255355.2</v>
+        <f>G22/G30</f>
+      </c>
+      <c r="M22" s="51"/>
+    </row>
+    <row r="23" spans="1:15" ht="18" customHeight="true">
+      <c r="A23" s="33"/>
+      <c r="B23" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="19">
+        <v>102</v>
+      </c>
+      <c r="G23" s="21">
+        <f>E23*F23*C32</f>
+      </c>
+      <c r="H23" s="29">
+        <f>SUM(G23:G23)</f>
       </c>
       <c r="I23" s="5">
-        <f>G23/G26</f>
-        <v>8.4395993877393272E-2</v>
-      </c>
-      <c r="J23" s="5"/>
+        <f>G23/G27</f>
+      </c>
+      <c r="J23" s="6"/>
       <c r="K23" s="6"/>
       <c r="L23" s="5">
-        <f>G23/G29</f>
-        <v>0.33693659586915981</v>
-      </c>
-      <c r="M23" s="9">
-        <f>H23/G26</f>
-        <v>8.4395993877393272E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>27</v>
+        <f>G23/G30</f>
+      </c>
+      <c r="M23" s="30">
+        <f>H23/G27</f>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="18" customHeight="true">
+      <c r="A24" s="33"/>
+      <c r="B24" s="17" t="s">
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" t="s">
+        <v>150</v>
       </c>
       <c r="F24">
-        <v>217200</v>
+        <v>102800</v>
       </c>
       <c r="G24" s="4">
         <f>E24*F24</f>
-        <v>217200</v>
-      </c>
-      <c r="H24" s="50">
-        <f>SUM(G24:G25)</f>
-        <v>365421.81449999998</v>
-      </c>
-      <c r="I24" s="6">
-        <f>G24/G26</f>
-        <v>7.1785535873833059E-2</v>
-      </c>
-      <c r="J24" s="6"/>
+      </c>
+      <c r="H24" s="4">
+        <f>SUM(G24)</f>
+      </c>
+      <c r="I24" s="5">
+        <f>G24/G27</f>
+      </c>
+      <c r="J24" s="5"/>
       <c r="K24" s="6"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="49">
-        <f>H24/G26</f>
-        <v>0.12077348422592504</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="12.6" x14ac:dyDescent="0.45">
-      <c r="A25" s="46"/>
-      <c r="B25" s="46"/>
+      <c r="L24" s="5">
+        <f>G24/G30</f>
+      </c>
+      <c r="M24" s="9">
+        <f>H24/G27</f>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="18" customHeight="true">
+      <c r="A25" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>26</v>
+      </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25" s="22">
-        <v>21975</v>
+      <c r="F25">
+        <v>168467</v>
       </c>
       <c r="G25" s="4">
-        <f>E25*F25*C31</f>
-        <v>148221.81450000001</v>
-      </c>
-      <c r="H25" s="33"/>
+        <f>E25*F25</f>
+      </c>
+      <c r="H25" s="38">
+        <f>SUM(G25:G26)</f>
+      </c>
       <c r="I25" s="6">
-        <f>G25/G26</f>
-        <v>4.8987948352091991E-2</v>
+        <f>G25/G27</f>
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="7"/>
-      <c r="M25" s="33"/>
-    </row>
-    <row r="26" spans="1:14" ht="12.6" x14ac:dyDescent="0.45">
-      <c r="A26" s="17" t="s">
+      <c r="M25" s="34">
+        <f>H25/G27</f>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="12.6">
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" s="22">
+        <v>11600</v>
+      </c>
+      <c r="G26" s="4">
+        <f>E26*F26*C32</f>
+      </c>
+      <c r="H26" s="35"/>
+      <c r="I26" s="6">
+        <f>G26/G27</f>
+      </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="35"/>
+    </row>
+    <row r="27" spans="1:15" ht="12.6">
+      <c r="A27" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="4">
+        <f>SUM(G2:G26)</f>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="6">
+        <f>SUM(I2:I24)</f>
+      </c>
+      <c r="J27" s="6">
+        <f>SUM(J2:J23)</f>
+      </c>
+      <c r="K27" s="6">
+        <f>SUM(K2:K23)</f>
+      </c>
+      <c r="L27" s="6">
+        <f>SUM(L2:L24)</f>
+      </c>
+      <c r="M27" s="6">
+        <f>SUM(M2:M26)</f>
+      </c>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:15" ht="12.6">
+      <c r="A28" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="G26" s="4">
-        <f>SUM(G2:G25)</f>
-        <v>3025679.1616313998</v>
-      </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="6">
-        <f>SUM(I2:I23)</f>
-        <v>0.87922651577407496</v>
-      </c>
-      <c r="J26" s="6">
-        <f>SUM(J2:J22)</f>
-        <v>1</v>
-      </c>
-      <c r="K26" s="6">
-        <f>SUM(K2:K22)</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="L26" s="6">
-        <f>SUM(L2:L23)</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="M26" s="6">
-        <f>SUM(M2:M25)</f>
-        <v>1</v>
-      </c>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="1:14" ht="12.6" x14ac:dyDescent="0.45">
-      <c r="A27" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="G28" s="4">
         <f>SUM(G5:G10)</f>
-        <v>601452.98</v>
-      </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" ht="12.6" x14ac:dyDescent="0.45">
-      <c r="A28" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" s="4">
-        <f>SUM(G2:G3,G11:G15)</f>
-        <v>1300931.2149400001</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="6"/>
@@ -2173,13 +2206,12 @@
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
     </row>
-    <row r="29" spans="1:14" ht="12.6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" ht="12.6">
       <c r="A29" s="17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G29" s="4">
-        <f>SUM(G4,G16:G23)</f>
-        <v>757873.15219140006</v>
+        <f>SUM(G2:G3,G11:G16)</f>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="6"/>
@@ -2188,17 +2220,13 @@
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
     </row>
-    <row r="30" spans="1:14" ht="12.6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:15" ht="12.6">
       <c r="A30" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30">
-        <v>0.85965999999999998</v>
-      </c>
-      <c r="G30" s="10"/>
+        <v>32</v>
+      </c>
+      <c r="G30" s="4">
+        <f>SUM(G4,G17:G24)</f>
+      </c>
       <c r="H30" s="10"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
@@ -2206,13 +2234,15 @@
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
     </row>
-    <row r="31" spans="1:14" ht="12.6" x14ac:dyDescent="0.45">
-      <c r="A31" s="17"/>
+    <row r="31" spans="1:15" ht="12.6">
+      <c r="A31" s="17" t="s">
+        <v>33</v>
+      </c>
       <c r="B31" s="17" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C31">
-        <v>6.7450200000000002</v>
+        <v>0.85102</v>
       </c>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
@@ -2222,12 +2252,13 @@
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
     </row>
-    <row r="32" spans="1:14" ht="12.6" x14ac:dyDescent="0.45">
-      <c r="A32" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
+    <row r="32" spans="1:15" ht="12.6">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32">
+        <v>6.6779099999999998</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
@@ -2237,8 +2268,13 @@
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
     </row>
-    <row r="33" spans="1:13" ht="12.6" x14ac:dyDescent="0.45">
-      <c r="A33" s="17"/>
+    <row r="33" spans="1:13" ht="12.6">
+      <c r="A33" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" t="s">
+        <v>134</v>
+      </c>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="6"/>
@@ -2247,132 +2283,138 @@
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
     </row>
-    <row r="34" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" s="18" t="s">
+    <row r="34" spans="1:13" ht="12.6">
+      <c r="A34" s="17"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+    </row>
+    <row r="35" spans="1:13" ht="18" customHeight="true">
+      <c r="A35" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="F34">
+      <c r="B35" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35">
         <v>677.7</v>
       </c>
-      <c r="G34" s="6">
-        <f>(E2-F34)/F34</f>
-        <v>-0.35074516747823525</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B35" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="F35">
+      <c r="G35" s="6">
+        <f>(E2-F35)/F35</f>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="18" customHeight="true">
+      <c r="B36" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36">
         <v>185.2</v>
       </c>
-      <c r="G35" s="6">
-        <f>(E3-F35)/F35</f>
-        <v>-0.35259179265658741</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="G36" s="27">
-        <f>G35-G34</f>
-        <v>-1.846625178352157E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G36" s="6">
+        <f>(E3-F36)/F36</f>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="18" customHeight="true">
       <c r="B37" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="G37" s="6">
-        <f>(1.02*3+0.92*3+0.87*2)/8-1</f>
-        <v>-5.4999999999999938E-2</v>
-      </c>
-      <c r="H37" s="6">
-        <f>G36-G37</f>
-        <v>5.3153374821647781E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="17" t="s">
-        <v>99</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="G37" s="27">
+        <f>G36-G35</f>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="18" customHeight="true">
       <c r="B38" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="F38">
+      <c r="G38" s="6">
+        <f>(1.02*3+0.92*3+0.87*2)/8-1</f>
+      </c>
+      <c r="H38" s="27">
+        <f>G37-G38</f>
+      </c>
+      <c r="I38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="18" customHeight="true">
+      <c r="A39" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F39">
         <v>449</v>
       </c>
-      <c r="G38" s="6">
-        <f>(E2-F38)/F38</f>
-        <v>-2.0044543429844099E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="F39">
+      <c r="G39" s="6">
+        <f>(E2-F39)/F39</f>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="18" customHeight="true">
+      <c r="B40" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F40">
         <v>396</v>
       </c>
-      <c r="G39" s="6">
-        <f>(E10-F39)/F39</f>
-        <v>-5.2272727272727098E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G40" s="27">
-        <f>G39-G38</f>
-        <v>1.481727070257139E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G40" s="6">
+        <f>(E10-F40)/F40</f>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="18" customHeight="true">
       <c r="B41" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G41" s="6">
-        <f>(0-9%)/2</f>
-        <v>-4.4999999999999998E-2</v>
-      </c>
-      <c r="H41" s="6">
-        <f>G40-G41</f>
-        <v>5.9817270702571389E-2</v>
+        <v>92</v>
+      </c>
+      <c r="G41" s="27">
+        <f>G40-G39</f>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="18" customHeight="true">
+      <c r="B42" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G42" s="6">
+        <f>(0-9%-20%)/3</f>
+      </c>
+      <c r="H42" s="27">
+        <f>G41-G42</f>
+      </c>
+      <c r="I42" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A16:A23"/>
-    <mergeCell ref="M24:M25"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="M2:M4"/>
+    <mergeCell ref="M8:M10"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="M11:M16"/>
+    <mergeCell ref="M17:M22"/>
+    <mergeCell ref="H17:H22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="H11:H16"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="H8:H10"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="H5:H7"/>
-    <mergeCell ref="M5:M7"/>
-    <mergeCell ref="M2:M4"/>
-    <mergeCell ref="M8:M10"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="M11:M15"/>
-    <mergeCell ref="M16:M21"/>
-    <mergeCell ref="H16:H21"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="H11:H15"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="A17:A24"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="H25:H26"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>